--- a/inst/resources/tool_obs_community_iphra_v2.xlsx
+++ b/inst/resources/tool_obs_community_iphra_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'survey'!$B$1:$M$19</definedName>
@@ -731,7 +731,21 @@
           <t>start</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>début</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>البداية</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>inicio</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>start</t>
@@ -752,7 +766,21 @@
           <t>end</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>النهاية</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>end</t>
@@ -773,7 +801,21 @@
           <t>today</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>aujourd’hui</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>اليوم</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>hoy</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>today</t>
@@ -794,7 +836,21 @@
           <t>deviceid</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>identifiant de l’appareil</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>معرّف الجهاز</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>identificador del dispositivo</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>deviceid</t>
@@ -815,7 +871,21 @@
           <t>audit</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>journal d’audit</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>سجل التدقيق</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>registro de auditoría</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>audit</t>
@@ -842,9 +912,21 @@
           <t>date_survey</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Quelle est la date de l’entretien ?</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>ما هو تاريخ المقابلة؟</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuál es la fecha de la entrevista?</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="n"/>
       <c r="J7" t="inlineStr">
         <is>
@@ -879,8 +961,21 @@
           <t>enumerator</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Veuillez indiquer l’identifiant de l’enquêteur</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>يرجى تحديد معرف الباحث الميداني</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Por favor indique el identificador del encuestador</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Please specify enumerator ID</t>
@@ -904,8 +999,21 @@
           <t>site1</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
-      <c r="F9" s="2" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Veuillez indiquer le site de l’étude</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>يرجى تحديد موقع الدراسة</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Por favor indique el sitio del estudio</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Please specify study site</t>
@@ -929,16 +1037,29 @@
           <t>gps_coordinates</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Veuillez fournir les coordonnées GPS du point de départ</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>(Appuyer sur l'icône de détection de la position actuelle)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>يرجى تقديم إحداثيات GPS لنقطة البداية</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>(انقر على أيقونة اكتشاف الموقع الحالي)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Por favor proporcione las coordenadas GPS del punto de inicio</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -974,9 +1095,22 @@
           <t>social_home_obs</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Observez-vous des personnes présentes à domicile ?</t>
+        </is>
+      </c>
       <c r="E11" s="7" t="n"/>
-      <c r="F11" s="2" t="n"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>هل تلاحظ وجود أشخاص في المنازل؟</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>¿Observa personas en sus hogares?</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">Do you observe people at home? </t>
@@ -1014,9 +1148,22 @@
           <t>service_access_obs</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Existe-t-il des zones de la communauté ayant des niveaux d’accès différents aux services d’eau, d’assainissement ou autres ?</t>
+        </is>
+      </c>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="2" t="n"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>هل توجد أجزاء من المجتمع لديها مستويات مختلفة من الوصول إلى المياه أو الصرف الصحي أو الخدمات الأخرى؟</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>¿Hay partes de la comunidad con diferentes niveles de acceso a agua, saneamiento u otros servicios?</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Are there any parts of the community that appear to have different levels of access to water, sanitation, or other services?</t>
@@ -1051,9 +1198,22 @@
           <t>response_activities_obs</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Y a-t-il des activités de réponse en cours (gouvernement, ONG ou autres) ?</t>
+        </is>
+      </c>
       <c r="E13" s="7" t="n"/>
-      <c r="F13" s="2" t="n"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>هل توجد أنشطة استجابة جارية من قبل الحكومة أو المنظمات غير الحكومية أو جهات أخرى؟</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>¿Hay actividades de respuesta en curso (gobierno, ONG u otras)?</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">Are there any government, NGO or other response activities going on? </t>
@@ -1090,9 +1250,22 @@
           <t>damage_obs</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Y a-t-il des débris ou des gravats provenant de bâtiments détruits ou endommagés ?</t>
+        </is>
+      </c>
       <c r="E14" s="7" t="n"/>
-      <c r="F14" s="2" t="n"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>هل توجد أنقاض أو حطام من مبانٍ مدمرة أو متضررة؟</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>¿Hay escombros de edificios destruidos o dañados?</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Are there any debris/rubble from destroyed or damaged building?</t>
@@ -1129,9 +1302,22 @@
           <t>stagnant_flood_obs</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Y a-t-il de l’eau stagnante ou des zones submergées ?</t>
+        </is>
+      </c>
       <c r="E15" s="7" t="n"/>
-      <c r="F15" s="2" t="n"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>هل توجد مياه راكدة أو مناطق مغمورة بالمياه؟</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>¿Hay agua estancada o zonas inundadas?</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Is there any stagnant water or areas submerged by water?</t>
@@ -1169,9 +1355,22 @@
           <t>biological_chemical_threats</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Existe-t-il des menaces biologiques ou chimiques graves pour la santé publique visibles dans l’espace public ?</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
-      <c r="F16" s="2" t="n"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>هل توجد تهديدات بيولوجية أو كيميائية خطيرة للصحة العامة ظاهرة في الأماكن العامة؟</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>¿Existen amenazas biológicas o químicas graves para la salud pública visibles en espacios públicos?</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>Are there serious biological or chemical threats to public health exposed in public?</t>
@@ -1209,9 +1408,22 @@
           <t>solid_waste_threats</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Y a-t-il des amas visibles de déchets solides ou d’ordures dans la communauté ?</t>
+        </is>
+      </c>
       <c r="E17" s="7" t="n"/>
-      <c r="F17" s="2" t="n"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>هل توجد أكوام مرئية من النفايات الصلبة أو القمامة في المجتمع؟</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>¿Hay montones visibles de residuos sólidos o basura en la comunidad?</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">Are there visible piles of solid waste / garbage in the community? </t>
@@ -1247,9 +1459,22 @@
           <t>other_threats</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Avez-vous observé d’autres menaces pour la santé publique ?</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>هل لاحظت أي تهديدات أخرى للصحة العامة؟</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>¿Ha observado otras amenazas para la salud pública?</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Are there any other threats to public health you have observed?</t>
@@ -1283,7 +1508,21 @@
           <t>comment</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Y a-t-il d’autres commentaires ou observations concernant l’état ou la qualité de ce point d’eau ?</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>هل توجد أي ملاحظات أخرى حول حالة أو جودة نقطة المياه هذه؟</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>¿Hay otros comentarios u observaciones sobre el estado o la calidad de este punto de agua?</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">Is there any other comment or observation on the status or quality of this water point? </t>
@@ -1371,7 +1610,7 @@
     <row r="98">
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1379,7 +1618,7 @@
       <c r="D99" s="2" t="n"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>

--- a/inst/resources/tool_obs_community_iphra_v2.xlsx
+++ b/inst/resources/tool_obs_community_iphra_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'survey'!$B$1:$M$19</definedName>
@@ -638,42 +638,42 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>label::French (fr)</t>
+          <t>label::French</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>hint::French (fr)</t>
+          <t>hint::French</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>label::Arabic (ar)</t>
+          <t>label::Arabic</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>hint::Arabic (ar)</t>
+          <t>hint::Arabic</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>label::Spanish (sp)</t>
+          <t>label::Spanish</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>hint::Spanish (sp)</t>
+          <t>hint::Spanish</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>label::English (en)</t>
+          <t>label::English</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>hint::English (en)</t>
+          <t>hint::English</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -1529,88 +1529,10 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
     <row r="98">
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -1618,7 +1540,7 @@
       <c r="D99" s="2" t="n"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -1665,22 +1587,22 @@
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>label::French (fr)</t>
+          <t>label::French</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>label::Arabic (ar)</t>
+          <t>label::Arabic</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>label::Spanish (sp)</t>
+          <t>label::Spanish</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>label::English (en)</t>
+          <t>label::English</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2741,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>English (en)</t>
+          <t>English</t>
         </is>
       </c>
     </row>
